--- a/艾宾浩斯.xlsx
+++ b/艾宾浩斯.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="高数" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="35">
   <si>
     <t>高数基础18讲</t>
   </si>
@@ -139,6 +139,12 @@
   </si>
   <si>
     <t>第1~2课</t>
+  </si>
+  <si>
+    <t>第3~4课</t>
+  </si>
+  <si>
+    <t>基本使用</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1315,7 @@
       </c>
       <c r="P7" s="1">
         <f ca="1">TODAY()-I7</f>
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1362,7 +1368,7 @@
       </c>
       <c r="P9" s="1">
         <f ca="1">TODAY()-I9</f>
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1415,7 +1421,7 @@
       </c>
       <c r="P11" s="1">
         <f ca="1">TODAY()-I11</f>
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1544,7 +1550,7 @@
       </c>
       <c r="P17" s="1">
         <f ca="1">TODAY()-I17</f>
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1597,7 +1603,7 @@
       </c>
       <c r="P19" s="1">
         <f ca="1">TODAY()-I19</f>
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1650,7 +1656,7 @@
       </c>
       <c r="P21" s="1">
         <f ca="1">TODAY()-I21</f>
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1779,7 +1785,7 @@
       </c>
       <c r="P27" s="1">
         <f ca="1">TODAY()-I27</f>
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -1832,7 +1838,7 @@
       </c>
       <c r="P29" s="1">
         <f ca="1">TODAY()-I29</f>
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -1885,7 +1891,7 @@
       </c>
       <c r="P31" s="1">
         <f ca="1">TODAY()-I31</f>
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2035,7 +2041,7 @@
       </c>
       <c r="O37" s="1">
         <f ca="1">TODAY()-I37</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P37" s="1"/>
     </row>
@@ -2086,7 +2092,7 @@
       </c>
       <c r="O39" s="1">
         <f ca="1">TODAY()-I39</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P39" s="1"/>
     </row>
@@ -2239,7 +2245,7 @@
       <c r="J47" s="3"/>
       <c r="K47" s="1">
         <f ca="1">TODAY()-I47</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -2590,7 +2596,7 @@
       </c>
       <c r="L3" s="1">
         <f ca="1">TODAY()-I3</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -3790,7 +3796,7 @@
       </c>
       <c r="L5" s="1">
         <f ca="1">TODAY()-I5</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -3832,11 +3838,11 @@
       <c r="J7" s="3"/>
       <c r="K7" s="1">
         <f ca="1">TODAY()-I7</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7" s="1">
         <f ca="1">TODAY()-I7</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -4899,11 +4905,13 @@
         <v>46301</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="1">
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1">
         <f ca="1">TODAY()-I3</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="1"/>
+        <v>1</v>
+      </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -4928,7 +4936,9 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -4936,10 +4946,18 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="6"/>
+      <c r="I5" s="6">
+        <v>46302</v>
+      </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="K5" s="1">
+        <f ca="1">TODAY()-I5</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <f ca="1">TODAY()-I5</f>
+        <v>0</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -5910,9 +5928,6 @@
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="I1:J2"/>
     <mergeCell ref="A3:H4"/>
-    <mergeCell ref="I3:J4"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="I5:J6"/>
     <mergeCell ref="A7:H8"/>
     <mergeCell ref="I7:J8"/>
     <mergeCell ref="A9:H10"/>
@@ -5957,6 +5972,9 @@
     <mergeCell ref="I47:J48"/>
     <mergeCell ref="A49:H50"/>
     <mergeCell ref="I49:J50"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="I5:J6"/>
+    <mergeCell ref="A5:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -6024,7 +6042,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6034,14 +6052,17 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="6">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="1">
         <f ca="1">TODAY()-I3</f>
         <v>0</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="L3" s="1">
+        <f ca="1">TODAY()-I3</f>
+        <v>0</v>
+      </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>

--- a/艾宾浩斯.xlsx
+++ b/艾宾浩斯.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="高数" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="36">
   <si>
     <t>高数基础18讲</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>第3~4课</t>
+  </si>
+  <si>
+    <t>第5~6课</t>
   </si>
   <si>
     <t>基本使用</t>
@@ -1315,7 +1318,7 @@
       </c>
       <c r="P7" s="1">
         <f ca="1">TODAY()-I7</f>
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1368,7 +1371,7 @@
       </c>
       <c r="P9" s="1">
         <f ca="1">TODAY()-I9</f>
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1421,7 +1424,7 @@
       </c>
       <c r="P11" s="1">
         <f ca="1">TODAY()-I11</f>
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1550,7 +1553,7 @@
       </c>
       <c r="P17" s="1">
         <f ca="1">TODAY()-I17</f>
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1603,7 +1606,7 @@
       </c>
       <c r="P19" s="1">
         <f ca="1">TODAY()-I19</f>
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1656,7 +1659,7 @@
       </c>
       <c r="P21" s="1">
         <f ca="1">TODAY()-I21</f>
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1785,7 +1788,7 @@
       </c>
       <c r="P27" s="1">
         <f ca="1">TODAY()-I27</f>
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -1838,7 +1841,7 @@
       </c>
       <c r="P29" s="1">
         <f ca="1">TODAY()-I29</f>
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -1891,7 +1894,7 @@
       </c>
       <c r="P31" s="1">
         <f ca="1">TODAY()-I31</f>
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2041,7 +2044,7 @@
       </c>
       <c r="O37" s="1">
         <f ca="1">TODAY()-I37</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P37" s="1"/>
     </row>
@@ -2092,7 +2095,7 @@
       </c>
       <c r="O39" s="1">
         <f ca="1">TODAY()-I39</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P39" s="1"/>
     </row>
@@ -2245,7 +2248,7 @@
       <c r="J47" s="3"/>
       <c r="K47" s="1">
         <f ca="1">TODAY()-I47</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -2596,7 +2599,7 @@
       </c>
       <c r="L3" s="1">
         <f ca="1">TODAY()-I3</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -3796,7 +3799,7 @@
       </c>
       <c r="L5" s="1">
         <f ca="1">TODAY()-I5</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -3838,11 +3841,11 @@
       <c r="J7" s="3"/>
       <c r="K7" s="1">
         <f ca="1">TODAY()-I7</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="1">
         <f ca="1">TODAY()-I7</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -4910,7 +4913,7 @@
       </c>
       <c r="L3" s="1">
         <f ca="1">TODAY()-I3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -4950,13 +4953,12 @@
         <v>46302</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="1">
-        <f ca="1">TODAY()-I5</f>
-        <v>0</v>
+      <c r="K5" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="L5" s="1">
         <f ca="1">TODAY()-I5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -4982,7 +4984,9 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -4990,10 +4994,18 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="6"/>
+      <c r="I7" s="6">
+        <v>46303</v>
+      </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="K7" s="1">
+        <f ca="1">TODAY()-I7</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <f ca="1">TODAY()-I7</f>
+        <v>0</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -5928,8 +5940,6 @@
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="I1:J2"/>
     <mergeCell ref="A3:H4"/>
-    <mergeCell ref="A7:H8"/>
-    <mergeCell ref="I7:J8"/>
     <mergeCell ref="A9:H10"/>
     <mergeCell ref="I9:J10"/>
     <mergeCell ref="A11:H12"/>
@@ -5975,6 +5985,8 @@
     <mergeCell ref="I3:J4"/>
     <mergeCell ref="I5:J6"/>
     <mergeCell ref="A5:H6"/>
+    <mergeCell ref="A7:H8"/>
+    <mergeCell ref="I7:J8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -6042,7 +6054,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6057,11 +6069,11 @@
       <c r="J3" s="3"/>
       <c r="K3" s="1">
         <f ca="1">TODAY()-I3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1">
         <f ca="1">TODAY()-I3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>

--- a/艾宾浩斯.xlsx
+++ b/艾宾浩斯.xlsx
@@ -9,18 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="14400" windowHeight="12255" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="高数" sheetId="1" r:id="rId1"/>
     <sheet name="线代" sheetId="4" r:id="rId2"/>
-    <sheet name="python" sheetId="3" r:id="rId3"/>
-    <sheet name="mysql必知必会" sheetId="12" r:id="rId4"/>
-    <sheet name="GIT学习" sheetId="14" r:id="rId5"/>
-    <sheet name="数据结构" sheetId="7" r:id="rId6"/>
-    <sheet name="计算机组成原理" sheetId="8" r:id="rId7"/>
-    <sheet name="计算机网络" sheetId="9" r:id="rId8"/>
-    <sheet name="操作系统" sheetId="10" r:id="rId9"/>
+    <sheet name="英语语法" sheetId="16" r:id="rId3"/>
+    <sheet name="python" sheetId="3" r:id="rId4"/>
+    <sheet name="mysql必知必会" sheetId="12" r:id="rId5"/>
+    <sheet name="GIT学习" sheetId="14" r:id="rId6"/>
+    <sheet name="数据结构" sheetId="7" r:id="rId7"/>
+    <sheet name="计算机组成原理" sheetId="8" r:id="rId8"/>
+    <sheet name="计算机网络" sheetId="9" r:id="rId9"/>
+    <sheet name="操作系统" sheetId="10" r:id="rId10"/>
+    <sheet name="mysql必知必会 (2)" sheetId="15" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="38">
   <si>
     <t>高数基础18讲</t>
   </si>
@@ -126,6 +128,9 @@
     <t>线代基础6讲</t>
   </si>
   <si>
+    <t>英语语法</t>
+  </si>
+  <si>
     <t>学习内容</t>
   </si>
   <si>
@@ -145,6 +150,9 @@
   </si>
   <si>
     <t>第5~6课</t>
+  </si>
+  <si>
+    <t>第7~8课</t>
   </si>
   <si>
     <t>基本使用</t>
@@ -1318,7 +1326,7 @@
       </c>
       <c r="P7" s="1">
         <f ca="1">TODAY()-I7</f>
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1371,7 +1379,7 @@
       </c>
       <c r="P9" s="1">
         <f ca="1">TODAY()-I9</f>
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1424,7 +1432,7 @@
       </c>
       <c r="P11" s="1">
         <f ca="1">TODAY()-I11</f>
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1553,7 +1561,7 @@
       </c>
       <c r="P17" s="1">
         <f ca="1">TODAY()-I17</f>
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1606,7 +1614,7 @@
       </c>
       <c r="P19" s="1">
         <f ca="1">TODAY()-I19</f>
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1659,7 +1667,7 @@
       </c>
       <c r="P21" s="1">
         <f ca="1">TODAY()-I21</f>
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1788,7 +1796,7 @@
       </c>
       <c r="P27" s="1">
         <f ca="1">TODAY()-I27</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -1841,7 +1849,7 @@
       </c>
       <c r="P29" s="1">
         <f ca="1">TODAY()-I29</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -1894,7 +1902,7 @@
       </c>
       <c r="P31" s="1">
         <f ca="1">TODAY()-I31</f>
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2044,7 +2052,7 @@
       </c>
       <c r="O37" s="1">
         <f ca="1">TODAY()-I37</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P37" s="1"/>
     </row>
@@ -2095,7 +2103,7 @@
       </c>
       <c r="O39" s="1">
         <f ca="1">TODAY()-I39</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P39" s="1"/>
     </row>
@@ -2248,7 +2256,7 @@
       <c r="J47" s="3"/>
       <c r="K47" s="1">
         <f ca="1">TODAY()-I47</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -2521,7 +2529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P50"/>
@@ -2529,7 +2537,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2580,6 +2588,2296 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="200">
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="L33:L34"/>
+    <mergeCell ref="L35:L36"/>
+    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="L41:L42"/>
+    <mergeCell ref="L43:L44"/>
+    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="M33:M34"/>
+    <mergeCell ref="M35:M36"/>
+    <mergeCell ref="M37:M38"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="M41:M42"/>
+    <mergeCell ref="M43:M44"/>
+    <mergeCell ref="M45:M46"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="N33:N34"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="N43:N44"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="O27:O28"/>
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="P33:P34"/>
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="P39:P40"/>
+    <mergeCell ref="P41:P42"/>
+    <mergeCell ref="P43:P44"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="P49:P50"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="I5:J6"/>
+    <mergeCell ref="A7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="A9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="A11:H12"/>
+    <mergeCell ref="I11:J12"/>
+    <mergeCell ref="A13:H14"/>
+    <mergeCell ref="I13:J14"/>
+    <mergeCell ref="A15:H16"/>
+    <mergeCell ref="I15:J16"/>
+    <mergeCell ref="A17:H18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="A19:H20"/>
+    <mergeCell ref="I19:J20"/>
+    <mergeCell ref="A21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="A23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="A25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="A27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="A29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="A31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="A33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="A35:H36"/>
+    <mergeCell ref="I35:J36"/>
+    <mergeCell ref="A37:H38"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="A39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="A41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="A43:H44"/>
+    <mergeCell ref="I43:J44"/>
+    <mergeCell ref="A45:H46"/>
+    <mergeCell ref="I45:J46"/>
+    <mergeCell ref="A47:H48"/>
+    <mergeCell ref="I47:J48"/>
+    <mergeCell ref="A49:H50"/>
+    <mergeCell ref="I49:J50"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3"/>
+      <c r="K1" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2</v>
+      </c>
+      <c r="M1" s="1">
+        <v>4</v>
+      </c>
+      <c r="N1" s="1">
+        <v>7</v>
+      </c>
+      <c r="O1" s="1">
+        <v>15</v>
+      </c>
+      <c r="P1" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="6">
+        <v>46301</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1">
+        <f ca="1" t="shared" ref="L3:L7" si="0">TODAY()-I3</f>
+        <v>3</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="6">
+        <v>46302</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="1">
+        <f ca="1" t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="6">
+        <v>46303</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="1">
+        <f ca="1">TODAY()-I7</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <f ca="1" t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="200">
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="L33:L34"/>
+    <mergeCell ref="L35:L36"/>
+    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="L41:L42"/>
+    <mergeCell ref="L43:L44"/>
+    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="M33:M34"/>
+    <mergeCell ref="M35:M36"/>
+    <mergeCell ref="M37:M38"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="M41:M42"/>
+    <mergeCell ref="M43:M44"/>
+    <mergeCell ref="M45:M46"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="N33:N34"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="N43:N44"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="O27:O28"/>
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="P33:P34"/>
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="P39:P40"/>
+    <mergeCell ref="P41:P42"/>
+    <mergeCell ref="P43:P44"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="P49:P50"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="I5:J6"/>
+    <mergeCell ref="A7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="A9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="A11:H12"/>
+    <mergeCell ref="I11:J12"/>
+    <mergeCell ref="A13:H14"/>
+    <mergeCell ref="I13:J14"/>
+    <mergeCell ref="A15:H16"/>
+    <mergeCell ref="I15:J16"/>
+    <mergeCell ref="A17:H18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="A19:H20"/>
+    <mergeCell ref="I19:J20"/>
+    <mergeCell ref="A21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="A23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="A25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="A27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="A29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="A31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="A33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="A35:H36"/>
+    <mergeCell ref="I35:J36"/>
+    <mergeCell ref="A37:H38"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="A39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="A41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="A43:H44"/>
+    <mergeCell ref="I43:J44"/>
+    <mergeCell ref="A45:H46"/>
+    <mergeCell ref="I45:J46"/>
+    <mergeCell ref="A47:H48"/>
+    <mergeCell ref="I47:J48"/>
+    <mergeCell ref="A49:H50"/>
+    <mergeCell ref="I49:J50"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3"/>
+      <c r="K1" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2</v>
+      </c>
+      <c r="M1" s="1">
+        <v>4</v>
+      </c>
+      <c r="N1" s="1">
+        <v>7</v>
+      </c>
+      <c r="O1" s="1">
+        <v>15</v>
+      </c>
+      <c r="P1" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2599,7 +4897,7 @@
       </c>
       <c r="L3" s="1">
         <f ca="1">TODAY()-I3</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -3730,9 +6028,7 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -3742,24 +6038,12 @@
       <c r="H3" s="1"/>
       <c r="I3" s="6"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1"/>
@@ -3780,9 +6064,7 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -3790,17 +6072,10 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="6">
-        <v>46278</v>
-      </c>
+      <c r="I5" s="2"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L5" s="1">
-        <f ca="1">TODAY()-I5</f>
-        <v>25</v>
-      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -3825,9 +6100,7 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -3835,18 +6108,10 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="6">
-        <v>46279</v>
-      </c>
+      <c r="I7" s="6"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="1">
-        <f ca="1">TODAY()-I7</f>
-        <v>24</v>
-      </c>
-      <c r="L7" s="1">
-        <f ca="1">TODAY()-I7</f>
-        <v>24</v>
-      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -4843,7 +7108,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4895,7 +7160,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4904,21 +7169,26 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="6">
-        <v>46301</v>
-      </c>
+      <c r="I3" s="6"/>
       <c r="J3" s="3"/>
       <c r="K3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="1">
-        <f ca="1">TODAY()-I3</f>
-        <v>2</v>
-      </c>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1"/>
@@ -4940,7 +7210,7 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -4950,7 +7220,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="6">
-        <v>46302</v>
+        <v>46278</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="1" t="s">
@@ -4958,7 +7228,7 @@
       </c>
       <c r="L5" s="1">
         <f ca="1">TODAY()-I5</f>
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -4985,7 +7255,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -4995,16 +7265,16 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="6">
-        <v>46303</v>
+        <v>46279</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="1">
         <f ca="1">TODAY()-I7</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L7" s="1">
         <f ca="1">TODAY()-I7</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -5042,6 +7312,1176 @@
       <c r="J9" s="3"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="200">
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="L33:L34"/>
+    <mergeCell ref="L35:L36"/>
+    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="L41:L42"/>
+    <mergeCell ref="L43:L44"/>
+    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="M33:M34"/>
+    <mergeCell ref="M35:M36"/>
+    <mergeCell ref="M37:M38"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="M41:M42"/>
+    <mergeCell ref="M43:M44"/>
+    <mergeCell ref="M45:M46"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="N33:N34"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="N43:N44"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="O27:O28"/>
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="P33:P34"/>
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="P39:P40"/>
+    <mergeCell ref="P41:P42"/>
+    <mergeCell ref="P43:P44"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="P49:P50"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="I5:J6"/>
+    <mergeCell ref="A7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="A9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="A11:H12"/>
+    <mergeCell ref="I11:J12"/>
+    <mergeCell ref="A13:H14"/>
+    <mergeCell ref="I13:J14"/>
+    <mergeCell ref="A15:H16"/>
+    <mergeCell ref="I15:J16"/>
+    <mergeCell ref="A17:H18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="A19:H20"/>
+    <mergeCell ref="I19:J20"/>
+    <mergeCell ref="A21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="A23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="A25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="A27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="A29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="A31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="A33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="A35:H36"/>
+    <mergeCell ref="I35:J36"/>
+    <mergeCell ref="A37:H38"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="A39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="A41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="A43:H44"/>
+    <mergeCell ref="I43:J44"/>
+    <mergeCell ref="A45:H46"/>
+    <mergeCell ref="I45:J46"/>
+    <mergeCell ref="A47:H48"/>
+    <mergeCell ref="I47:J48"/>
+    <mergeCell ref="A49:H50"/>
+    <mergeCell ref="I49:J50"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3"/>
+      <c r="K1" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2</v>
+      </c>
+      <c r="M1" s="1">
+        <v>4</v>
+      </c>
+      <c r="N1" s="1">
+        <v>7</v>
+      </c>
+      <c r="O1" s="1">
+        <v>15</v>
+      </c>
+      <c r="P1" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="6">
+        <v>46301</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" s="1">
+        <f ca="1">TODAY()-I3</f>
+        <v>3</v>
+      </c>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="6">
+        <v>46302</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="1">
+        <f ca="1">TODAY()-I5</f>
+        <v>2</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="6">
+        <v>46303</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="1">
+        <f ca="1">TODAY()-I7</f>
+        <v>1</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="6">
+        <v>46304</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="1">
+        <f ca="1">TODAY()-I9</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <f ca="1">TODAY()-I9</f>
+        <v>0</v>
+      </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -5994,7 +9434,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P50"/>
@@ -6002,7 +9442,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6054,7 +9494,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6069,1143 +9509,12 @@
       <c r="J3" s="3"/>
       <c r="K3" s="1">
         <f ca="1">TODAY()-I3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="1">
         <f ca="1">TODAY()-I3</f>
-        <v>1</v>
-      </c>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-    </row>
-    <row r="39" spans="1:16">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-    </row>
-    <row r="40" spans="1:16">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="1:16">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-    </row>
-    <row r="49" spans="1:16">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-    </row>
-    <row r="50" spans="1:16">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="200">
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="K27:K28"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="L33:L34"/>
-    <mergeCell ref="L35:L36"/>
-    <mergeCell ref="L37:L38"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="L41:L42"/>
-    <mergeCell ref="L43:L44"/>
-    <mergeCell ref="L45:L46"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="M27:M28"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="M33:M34"/>
-    <mergeCell ref="M35:M36"/>
-    <mergeCell ref="M37:M38"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="M41:M42"/>
-    <mergeCell ref="M43:M44"/>
-    <mergeCell ref="M45:M46"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="N27:N28"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="N31:N32"/>
-    <mergeCell ref="N33:N34"/>
-    <mergeCell ref="N35:N36"/>
-    <mergeCell ref="N37:N38"/>
-    <mergeCell ref="N39:N40"/>
-    <mergeCell ref="N41:N42"/>
-    <mergeCell ref="N43:N44"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="N49:N50"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="O27:O28"/>
-    <mergeCell ref="O29:O30"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="P19:P20"/>
-    <mergeCell ref="P21:P22"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="P27:P28"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="P31:P32"/>
-    <mergeCell ref="P33:P34"/>
-    <mergeCell ref="P35:P36"/>
-    <mergeCell ref="P37:P38"/>
-    <mergeCell ref="P39:P40"/>
-    <mergeCell ref="P41:P42"/>
-    <mergeCell ref="P43:P44"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="P49:P50"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="I3:J4"/>
-    <mergeCell ref="A5:H6"/>
-    <mergeCell ref="I5:J6"/>
-    <mergeCell ref="A7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="A9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="A11:H12"/>
-    <mergeCell ref="I11:J12"/>
-    <mergeCell ref="A13:H14"/>
-    <mergeCell ref="I13:J14"/>
-    <mergeCell ref="A15:H16"/>
-    <mergeCell ref="I15:J16"/>
-    <mergeCell ref="A17:H18"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="A19:H20"/>
-    <mergeCell ref="I19:J20"/>
-    <mergeCell ref="A21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="A23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="A25:H26"/>
-    <mergeCell ref="I25:J26"/>
-    <mergeCell ref="A27:H28"/>
-    <mergeCell ref="I27:J28"/>
-    <mergeCell ref="A29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="A31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="A33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="A35:H36"/>
-    <mergeCell ref="I35:J36"/>
-    <mergeCell ref="A37:H38"/>
-    <mergeCell ref="I37:J38"/>
-    <mergeCell ref="A39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="A41:H42"/>
-    <mergeCell ref="I41:J42"/>
-    <mergeCell ref="A43:H44"/>
-    <mergeCell ref="I43:J44"/>
-    <mergeCell ref="A45:H46"/>
-    <mergeCell ref="I45:J46"/>
-    <mergeCell ref="A47:H48"/>
-    <mergeCell ref="I47:J48"/>
-    <mergeCell ref="A49:H50"/>
-    <mergeCell ref="I49:J50"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
         <v>2</v>
       </c>
-      <c r="M1" s="1">
-        <v>4</v>
-      </c>
-      <c r="N1" s="1">
-        <v>7</v>
-      </c>
-      <c r="O1" s="1">
-        <v>15</v>
-      </c>
-      <c r="P1" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -8274,7 +10583,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9405,7 +11714,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10536,7 +12845,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
